--- a/artfynd/A 16103-2026 artfynd.xlsx
+++ b/artfynd/A 16103-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133471500</v>
+        <v>133471331</v>
       </c>
       <c r="B2" t="n">
         <v>57955</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504168</v>
+        <v>504149</v>
       </c>
       <c r="R2" t="n">
-        <v>6620215</v>
+        <v>6620203</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133471331</v>
+        <v>133471500</v>
       </c>
       <c r="B3" t="n">
         <v>57955</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504149</v>
+        <v>504168</v>
       </c>
       <c r="R3" t="n">
-        <v>6620203</v>
+        <v>6620215</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 16103-2026 artfynd.xlsx
+++ b/artfynd/A 16103-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133471331</v>
+        <v>133471500</v>
       </c>
       <c r="B2" t="n">
         <v>57955</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504149</v>
+        <v>504168</v>
       </c>
       <c r="R2" t="n">
-        <v>6620203</v>
+        <v>6620215</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133471500</v>
+        <v>133471331</v>
       </c>
       <c r="B3" t="n">
         <v>57955</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504168</v>
+        <v>504149</v>
       </c>
       <c r="R3" t="n">
-        <v>6620215</v>
+        <v>6620203</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 16103-2026 artfynd.xlsx
+++ b/artfynd/A 16103-2026 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>133471000</v>
       </c>
       <c r="B5" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16103-2026 artfynd.xlsx
+++ b/artfynd/A 16103-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133471500</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133471331</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>133471806</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>133471000</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16103-2026 artfynd.xlsx
+++ b/artfynd/A 16103-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133471500</v>
       </c>
       <c r="B2" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133471331</v>
       </c>
       <c r="B3" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>133471806</v>
       </c>
       <c r="B4" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>133471000</v>
       </c>
       <c r="B5" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16103-2026 artfynd.xlsx
+++ b/artfynd/A 16103-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133471500</v>
+        <v>133471331</v>
       </c>
       <c r="B2" t="n">
         <v>57972</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504168</v>
+        <v>504149</v>
       </c>
       <c r="R2" t="n">
-        <v>6620215</v>
+        <v>6620203</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133471331</v>
+        <v>133471500</v>
       </c>
       <c r="B3" t="n">
         <v>57972</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504149</v>
+        <v>504168</v>
       </c>
       <c r="R3" t="n">
-        <v>6620203</v>
+        <v>6620215</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 16103-2026 artfynd.xlsx
+++ b/artfynd/A 16103-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133471331</v>
+        <v>133471500</v>
       </c>
       <c r="B2" t="n">
         <v>57972</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504149</v>
+        <v>504168</v>
       </c>
       <c r="R2" t="n">
-        <v>6620203</v>
+        <v>6620215</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133471500</v>
+        <v>133471331</v>
       </c>
       <c r="B3" t="n">
         <v>57972</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504168</v>
+        <v>504149</v>
       </c>
       <c r="R3" t="n">
-        <v>6620215</v>
+        <v>6620203</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1014,7 +1014,7 @@
         <v>133471000</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16103-2026 artfynd.xlsx
+++ b/artfynd/A 16103-2026 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133471331</v>
+        <v>133471000</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Danshytte gård, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504149</v>
+        <v>504171</v>
       </c>
       <c r="R2" t="n">
-        <v>6620203</v>
+        <v>6620315</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133471500</v>
+        <v>133471331</v>
       </c>
       <c r="B3" t="n">
         <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504168</v>
+        <v>504149</v>
       </c>
       <c r="R3" t="n">
-        <v>6620215</v>
+        <v>6620203</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,14 +894,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133471806</v>
+        <v>133471500</v>
       </c>
       <c r="B4" t="n">
         <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -930,7 +925,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503994</v>
+        <v>504168</v>
       </c>
       <c r="R4" t="n">
-        <v>6620097</v>
+        <v>6620215</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,45 +1006,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133471000</v>
+        <v>133471806</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Danshytte gård, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504171</v>
+        <v>503994</v>
       </c>
       <c r="R5" t="n">
-        <v>6620315</v>
+        <v>6620097</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 16103-2026 artfynd.xlsx
+++ b/artfynd/A 16103-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133471000</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133471331</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133471500</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,8 +1135,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133471806</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>